--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487654_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487654_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8396</v>
+        <v>4.9096</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5277</v>
+        <v>6.388</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6881</v>
+        <v>-1.4785</v>
       </c>
       <c r="G2" t="n">
         <v>2.1356</v>
@@ -610,13 +610,13 @@
         <v>2.5224</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3219</v>
+        <v>1.3919</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1962</v>
+        <v>0.0566</v>
       </c>
       <c r="U2" t="n">
-        <v>2.1257</v>
+        <v>1.3353</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1702</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8294</v>
+        <v>3.5619</v>
       </c>
       <c r="E3" t="n">
-        <v>7.3425</v>
+        <v>6.8025</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.5131</v>
+        <v>-3.2406</v>
       </c>
       <c r="G3" t="n">
         <v>0.5105</v>
@@ -688,13 +688,13 @@
         <v>3.2985</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9354</v>
+        <v>0.6679</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6819</v>
+        <v>0.1418</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2535</v>
+        <v>0.526</v>
       </c>
       <c r="V3" t="n">
         <v>1.9955</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. VICENTE VIANA</t>
+          <t>C. UNANUE CEGARRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.878</v>
+        <v>2.8889</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2836</v>
+        <v>4.4882</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5944</v>
+        <v>-1.5992</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1722</v>
+        <v>-1.4955</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4096</v>
+        <v>-1.5851</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2375</v>
+        <v>0.0897</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6677</v>
+        <v>3.3848</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6271</v>
+        <v>0.4367</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0406</v>
+        <v>2.9481</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4956</v>
+        <v>-4.8803</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2175</v>
+        <v>-2.0218</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2781</v>
+        <v>-2.8585</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.194</v>
+        <v>0.9702</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7761</v>
+        <v>2.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>0.57</v>
+        <v>0.1949</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3039</v>
+        <v>-0.2981</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2661</v>
+        <v>0.493</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3299</v>
+        <v>3.2194</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2821</v>
+        <v>3.3418</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0478</v>
+        <v>-0.1224</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. UNANUE CEGARRA</t>
+          <t>A. VICENTE VIANA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7912</v>
+        <v>1.5688</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5267</v>
+        <v>1.0834</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7355</v>
+        <v>0.4854</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.4955</v>
+        <v>1.1722</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.5851</v>
+        <v>1.4096</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0897</v>
+        <v>-0.2375</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3848</v>
+        <v>1.6677</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4367</v>
+        <v>1.6271</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9481</v>
+        <v>0.0406</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.8803</v>
+        <v>-0.4956</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.0218</v>
+        <v>-0.2175</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.8585</v>
+        <v>-0.2781</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9702</v>
+        <v>-0.194</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R5" t="n">
-        <v>2.9105</v>
+        <v>0.7761</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9029</v>
+        <v>0.2608</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2596</v>
+        <v>0.1037</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3567</v>
+        <v>0.157</v>
       </c>
       <c r="V5" t="n">
-        <v>3.2194</v>
+        <v>0.3299</v>
       </c>
       <c r="W5" t="n">
-        <v>3.3418</v>
+        <v>0.2821</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1224</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.135</v>
+        <v>0.5593</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3904</v>
+        <v>-0.1296</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5254</v>
+        <v>0.6889</v>
       </c>
       <c r="G6" t="n">
         <v>1.2782</v>
@@ -922,13 +922,13 @@
         <v>0.3881</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.279</v>
+        <v>0.1452</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1817</v>
+        <v>0.0791</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0973</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2821</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. ABOUBACAR HIMA</t>
+          <t>B. GUEYE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0451</v>
+        <v>0.1847</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8056</v>
+        <v>0.9697</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8508</v>
+        <v>-0.785</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3108</v>
+        <v>-2.669</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6574</v>
+        <v>-0.6747</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9681999999999999</v>
+        <v>-1.9943</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4812</v>
+        <v>0.642</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3594</v>
+        <v>0.3172</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1218</v>
+        <v>0.3248</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.792</v>
+        <v>-3.311</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7019</v>
+        <v>-0.992</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.09</v>
+        <v>-2.3191</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.9403</v>
+        <v>1.3582</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9702</v>
+        <v>2.3284</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1045</v>
+        <v>-0.106</v>
       </c>
       <c r="T7" t="n">
-        <v>0.729</v>
+        <v>0.074</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3755</v>
+        <v>-0.18</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1015</v>
+        <v>1.6015</v>
       </c>
       <c r="W7" t="n">
-        <v>1.506</v>
+        <v>1.2239</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.4045</v>
+        <v>0.3776</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. GUEYE</t>
+          <t>S. ABOUBACAR HIMA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1272</v>
+        <v>-0.5367</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8486</v>
+        <v>0.2051</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9758</v>
+        <v>-0.7417</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.669</v>
+        <v>-0.3108</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6747</v>
+        <v>0.6574</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.9943</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>0.642</v>
+        <v>1.4812</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3172</v>
+        <v>1.3594</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3248</v>
+        <v>0.1218</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.311</v>
+        <v>-1.792</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.992</v>
+        <v>-0.7019</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.3191</v>
+        <v>-1.09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3582</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3284</v>
+        <v>0.9702</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4179</v>
+        <v>0.6129</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0471</v>
+        <v>0.1284</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3708</v>
+        <v>0.4845</v>
       </c>
       <c r="V8" t="n">
-        <v>1.6015</v>
+        <v>1.1015</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2239</v>
+        <v>1.506</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3776</v>
+        <v>-0.4045</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3165</v>
+        <v>-2.2014</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7174</v>
+        <v>-1.6569</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5991</v>
+        <v>-0.5446</v>
       </c>
       <c r="G9" t="n">
         <v>-1.2492</v>
@@ -1156,13 +1156,13 @@
         <v>0.3881</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4852</v>
+        <v>-0.3701</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1211</v>
+        <v>-0.0606</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3641</v>
+        <v>-0.3095</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.9855</v>
+        <v>-4.7731</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8319</v>
+        <v>-2.5106</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1535</v>
+        <v>-2.2626</v>
       </c>
       <c r="G10" t="n">
         <v>-3.7151</v>
@@ -1234,13 +1234,13 @@
         <v>2.3284</v>
       </c>
       <c r="S10" t="n">
-        <v>0.376</v>
+        <v>0.5883</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2894</v>
+        <v>0.0319</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6653</v>
+        <v>0.5563</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0642</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.3211</v>
+        <v>-4.8784</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1671</v>
+        <v>-1.8062</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.154</v>
+        <v>-3.0722</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6907</v>
@@ -1312,13 +1312,13 @@
         <v>1.5523</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7945</v>
+        <v>-0.3519</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5451</v>
+        <v>-0.1842</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2494</v>
+        <v>-0.1677</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4477</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6778000000000004</v>
+        <v>1.283600000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>13.2279</v>
+        <v>13.8336</v>
       </c>
       <c r="F12" t="n">
         <v>-12.5501</v>
@@ -1390,13 +1390,13 @@
         <v>17.463</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4283</v>
+        <v>3.0339</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.533</v>
+        <v>0.07260000000000003</v>
       </c>
       <c r="U12" t="n">
-        <v>2.961199999999999</v>
+        <v>2.9611</v>
       </c>
       <c r="V12" t="n">
         <v>4.283599999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.5987</v>
+        <v>5.2528</v>
       </c>
       <c r="E13" t="n">
-        <v>5.5407</v>
+        <v>5.1403</v>
       </c>
       <c r="F13" t="n">
-        <v>0.058</v>
+        <v>0.1125</v>
       </c>
       <c r="G13" t="n">
         <v>3.9513</v>
@@ -1468,13 +1468,13 @@
         <v>2.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3279</v>
+        <v>-0.0179</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3656</v>
+        <v>-0.0348</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0377</v>
+        <v>0.0168</v>
       </c>
       <c r="V13" t="n">
         <v>-1.591</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6656</v>
+        <v>3.7201</v>
       </c>
       <c r="E14" t="n">
         <v>4.4808</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8152</v>
+        <v>-0.7607</v>
       </c>
       <c r="G14" t="n">
         <v>1.1778</v>
@@ -1546,13 +1546,13 @@
         <v>1.3582</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3764</v>
+        <v>-0.3219</v>
       </c>
       <c r="T14" t="n">
         <v>-0.4845</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1081</v>
+        <v>0.1626</v>
       </c>
       <c r="V14" t="n">
         <v>1.506</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2986</v>
+        <v>1.3141</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4561</v>
+        <v>2.5562</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1575</v>
+        <v>-1.2421</v>
       </c>
       <c r="G15" t="n">
         <v>5.0152</v>
@@ -1624,13 +1624,13 @@
         <v>1.5523</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3046</v>
+        <v>-0.2891</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6662</v>
+        <v>-0.5661</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3616</v>
+        <v>0.2771</v>
       </c>
       <c r="V15" t="n">
         <v>0.8567</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. GUEYE</t>
+          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.5497</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6473</v>
+        <v>0.7799</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5482</v>
+        <v>-0.2302</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1905</v>
+        <v>2.2964</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1585</v>
+        <v>-0.6616</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.349</v>
+        <v>2.958</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7866</v>
+        <v>4.0561</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6776</v>
+        <v>0.1359</v>
       </c>
       <c r="L16" t="n">
-        <v>0.109</v>
+        <v>3.9201</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.9771</v>
+        <v>-1.7596</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5191</v>
+        <v>-0.7975</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.4581</v>
+        <v>-0.9621</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9702</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.9105</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9403</v>
+        <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>1.212</v>
+        <v>-0.6034</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5473</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6647</v>
+        <v>0.0443</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0478</v>
+        <v>-0.3672</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2239</v>
+        <v>0.2821</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1761</v>
+        <v>-0.6492</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
+          <t>K. SKUTYELNIK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0048</v>
+        <v>0.4432</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5797</v>
+        <v>1.4798</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5845</v>
+        <v>-1.0366</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2964</v>
+        <v>0.7249</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6616</v>
+        <v>-1.6469</v>
       </c>
       <c r="I17" t="n">
-        <v>2.958</v>
+        <v>2.3719</v>
       </c>
       <c r="J17" t="n">
-        <v>4.0561</v>
+        <v>1.6611</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1359</v>
+        <v>-0.8609</v>
       </c>
       <c r="L17" t="n">
-        <v>3.9201</v>
+        <v>2.522</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7596</v>
+        <v>-0.9362</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7975</v>
+        <v>-0.786</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9621</v>
+        <v>-0.1502</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7761</v>
+        <v>0.5821</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1344</v>
+        <v>1.5523</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1579</v>
+        <v>-0.1668</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8479</v>
+        <v>-0.1052</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.31</v>
+        <v>-0.0617</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3672</v>
+        <v>-0.697</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2821</v>
+        <v>0.894</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6492</v>
+        <v>-1.591</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. SKUTYELNIK</t>
+          <t>A. JIMÉNEZ BARRETO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2998</v>
+        <v>-0.1736</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9792999999999999</v>
+        <v>-0.5421</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2791</v>
+        <v>0.3685</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7249</v>
+        <v>-0.8946</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6469</v>
+        <v>-0.4358</v>
       </c>
       <c r="I18" t="n">
-        <v>2.3719</v>
+        <v>-0.4588</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6611</v>
+        <v>-0.4369</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8609</v>
+        <v>0.1442</v>
       </c>
       <c r="L18" t="n">
-        <v>2.522</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9362</v>
+        <v>-0.4577</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.786</v>
+        <v>-0.58</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1502</v>
+        <v>0.1223</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5821</v>
+        <v>1.5523</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>1.5523</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9098000000000001</v>
+        <v>-0.182</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6057</v>
+        <v>-0.1052</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3042</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.697</v>
+        <v>-0.6492</v>
       </c>
       <c r="W18" t="n">
-        <v>0.894</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.591</v>
+        <v>-0.6492</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. JIMÉNEZ BARRETO</t>
+          <t>S. GUEYE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7258</v>
+        <v>-0.8953</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0426</v>
+        <v>0.8465</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3168</v>
+        <v>-1.7418</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8946</v>
+        <v>-0.1905</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4358</v>
+        <v>2.1585</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4588</v>
+        <v>-2.349</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4369</v>
+        <v>2.7866</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1442</v>
+        <v>2.6776</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5810999999999999</v>
+        <v>0.109</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4577</v>
+        <v>-2.9771</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.58</v>
+        <v>-0.5191</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1223</v>
+        <v>-2.4581</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5523</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5523</v>
+        <v>1.9403</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7342</v>
+        <v>0.2176</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6057</v>
+        <v>-0.2535</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1285</v>
+        <v>0.4711</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6492</v>
+        <v>0.0478</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6492</v>
+        <v>-1.1761</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6858</v>
+        <v>-2.1318</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2353</v>
+        <v>-0.2652</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9212</v>
+        <v>-1.8666</v>
       </c>
       <c r="G20" t="n">
         <v>-0.3527</v>
@@ -2014,13 +2014,13 @@
         <v>1.9403</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6072</v>
+        <v>0.1612</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6079</v>
+        <v>0.1074</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0007</v>
+        <v>0.0538</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6516</v>
+        <v>-3.215</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0541</v>
+        <v>0.3544</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.7057</v>
+        <v>-3.5694</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4992</v>
@@ -2092,13 +2092,13 @@
         <v>1.3582</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6853</v>
+        <v>-0.2487</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5451</v>
+        <v>-0.2448</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1402</v>
+        <v>-0.0039</v>
       </c>
       <c r="V21" t="n">
         <v>-2.8254</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9721</v>
+        <v>-4.8748</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3808</v>
+        <v>-2.2807</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5913</v>
+        <v>-2.5941</v>
       </c>
       <c r="G22" t="n">
         <v>-4.1948</v>
@@ -2170,13 +2170,13 @@
         <v>1.1642</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4071</v>
+        <v>-0.3098</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7268</v>
+        <v>-0.6267</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3197</v>
+        <v>0.3169</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5642</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6779000000000002</v>
+        <v>-0.01060000000000105</v>
       </c>
       <c r="E23" t="n">
         <v>12.5499</v>
       </c>
       <c r="F23" t="n">
-        <v>-13.2279</v>
+        <v>-12.5605</v>
       </c>
       <c r="G23" t="n">
-        <v>6.033799999999998</v>
+        <v>6.0338</v>
       </c>
       <c r="H23" t="n">
         <v>2.6693</v>
@@ -2239,7 +2239,7 @@
         <v>-13.0135</v>
       </c>
       <c r="P23" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>-3.885780586188048e-16</v>
       </c>
       <c r="Q23" t="n">
         <v>-17.463</v>
@@ -2248,13 +2248,13 @@
         <v>17.463</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.4282</v>
+        <v>-1.7608</v>
       </c>
       <c r="T23" t="n">
         <v>-2.9611</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5327999999999999</v>
+        <v>1.2002</v>
       </c>
       <c r="V23" t="n">
         <v>-4.2835</v>
